--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2208,6 +2208,38 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Wed (2026-02-25)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0814 1068 3542 3847 4163 5890 6424 8286 8439 9431</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1511 2357 3115 4586 4965 6034 6445 6473 7266 8196</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2240,38 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sat (2026-02-28)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1002 3679 4256 4411 4486 5987 6901 7127 7232 7897</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0433 0515 2090 2546 4101 4473 4558 6202 8441 9542</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2272,6 +2272,38 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-01)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3927</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2607</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0318 0871 1083 1698 1854 2874 3869 4697 5609 8440</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0483 1995 2792 4408 6217 7338 7340 7953 9154 9595</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2304,6 +2304,38 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-04)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1271 1278 3102 3102 5117 5958 6587 7128 8183 9324</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1121 1394 2964 3616 4339 5612 7597 7609 8088 8251</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2336,38 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-07)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4146</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9274</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0456 1007 1255 3053 4227 4271 6558 7853 8388 9182</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0785 1427 2391 3206 4573 6337 6836 8642 9098 9321</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2368,6 +2368,38 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-08)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0220 1087 1424 3875 3974 4174 6036 6366 7578 9347</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0327 1233 1636 2173 3430 4280 4471 4533 6975 9541</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2400,6 +2400,38 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-11)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7905</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6773</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0073 0338 0732 0820 1651 2331 3707 3877 3927 7246</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1713 2090 3183 3958 4943 6373 7039 8830 9714 9927</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2432,6 +2432,38 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-14)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1366 1904 2415 4165 4899 5947 6695 6881 7273 9269</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0611 2413 3420 4059 4127 5803 8304 9391 9490 9561</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2464,6 +2464,38 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-15)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5747</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>9874</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0412 1147 1243 1985 2179 3468 6074 7024 8159 9891</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0691 2049 3591 3811 6162 6311 6915 8456 8658 9061</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -55,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -550,7 +551,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mon (2025-10-27)</t>
+          <t>Sun (2025-10-26)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,20 +583,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thu (2025-10-30)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2405</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>Wed (2025-10-29)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3378</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>0654</t>
         </is>
@@ -608,6 +605,2470 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>1855 3484 5091 5304 5580 7020 7468 8181 8389 9959</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sat (2025-11-01)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8483</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0055 1305 1313 2873 3170 3605 6544 6935 9121 9623</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0240 0666 2483 4559 4652 5216 7384 7462 9218 9662</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sun (2025-11-02)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8989</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0174 0593 1512 1880 3225 3794 7498 8969 9741 9788</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0563 0637 2654 5537 6570 7067 7154 7289 8277 8621</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wed (2025-11-05)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0180</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0851 1126 1441 1737 4295 4700 4987 6012 7459 9917</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0103 0309 0344 1491 2323 2375 2947 2997 4840 8837</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sat (2025-11-08)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6456</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0536</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0086 0874 1866 3240 6309 6425 6479 7497 9267 9995</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0547 0703 2634 4389 4767 4965 6069 6398 7817 8763</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sun (2025-11-09)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4528</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0013 0919 1843 5111 5448 6567 6889 7176 8035 9649</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0389 0735 1413 2238 4156 4847 5242 9274 9374 9944</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wed (2025-11-12)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9223</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8618</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0603 1786 3746 6852 7727 8023 8519 8726 8813 9364</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0329 2645 3015 3414 3888 4226 4335 4921 7747 8869</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sat (2025-11-15)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0781</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1021 2119 4606 5459 6276 7206 7642 8234 9635 9897</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0544 0709 0799 1824 3765 6952 8694 8817 8951 9577</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sun (2025-11-16)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7295</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1803 2867 2946 3263 4486 6618 7196 7561 7566 8307</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0138 1785 2390 3673 4834 5170 5762 6116 7906 9290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Wed (2025-11-19)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9551</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2131 2316 2335 3137 3262 4463 4648 5935 7783 8730</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1018 1474 2198 3011 6542 7733 8116 8422 8716 9908</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sat (2025-11-22)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5917</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1427 2554 3239 3389 4341 5669 8332 9772 9872 9972</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0521 0735 1081 1494 5700 5876 7413 8705 8837 9938</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sun (2025-11-23)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2755</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0520 2315 3723 4321 5001 5329 5380 5381 7849 8657</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2993 3756 3785 3906 4556 4665 4782 4790 7295 7405</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wed (2025-11-26)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2794</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0094 0578 0996 2636 4986 5250 5907 5935 6711 8675</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0939 4274 4307 6279 7839 8037 8225 8849 8968 9601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sat (2025-11-29)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7352</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1138 1451 2868 3446 3816 4748 8329 8340 8347 8776</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2611 4417 5138 5309 7373 7778 8581 9014 9746 9893</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sun (2025-11-30)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9245</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1207 1731 2286 2642 2686 4307 4987 6231 7490 8453</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0132 1287 1632 5096 5238 6029 6236 6414 7190 8301</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Wed (2025-12-03)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7331</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9746</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0631 1782 2639 2831 5018 5679 6543 6842 9325 9968</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0453 0703 1857 4805 5587 6005 8570 8914 8971 9708</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sat (2025-12-06)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7876</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0043 3875 4748 6877 7273 8373 8807 8855 8968 9175</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0711 1447 1982 3545 5764 5973 6437 7210 8735 9702</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sun (2025-12-07)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7370</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3433</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0788 0995 4095 4141 4928 5556 5874 6883 8494 8804</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2032 3456 5495 6576 7161 7479 7937 8155 9520 9808</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wed (2025-12-10)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2319 3782 3912 5652 6763 7204 8410 9019 9187 9793</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0610 0709 5029 5896 6168 6531 6776 9137 9349 9740</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sat (2025-12-13)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8789</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2060 3462 4944 5013 5259 6875 7659 8303 8898 9480</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0274 0404 0649 0932 1586 1600 4964 5388 7453 8147</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sun (2025-12-14)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7688</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2661 3079 3115 4136 4917 6091 6407 7364 8349 9780</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1055 2300 4417 5334 5675 6254 6494 6916 7259 8914</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Wed (2025-12-17)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8391</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4466</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2544 2824 4562 6642 7197 7913 8185 8207 8305 9892</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1194 1481 2476 3180 4232 5316 5925 6493 6896 8281</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sat (2025-12-20)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0093 0147 3818 3880 4052 5321 5432 5945 7065 8101</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2177 3103 3169 3626 3997 4853 6098 6917 7233 7273</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sun (2025-12-21)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1521 2763 3098 3970 4090 4474 5027 6891 8076 9987</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2448 2870 3331 5728 6851 7092 7198 7522 8518 9907</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wed (2025-12-24)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>9395</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>9492</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0791 0865 2850 3506 4939 8220 8301 8312 9169 9473</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0927 1156 1233 2731 3766 4199 5962 8319 9210 9274</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sat (2025-12-27)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>8780</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7854</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2581 2935 3191 6155 6485 7650 8132 8612 8718 9751</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0174 1271 1352 2226 2389 2534 2573 6096 6997 9815</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sun (2025-12-28)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>9507</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>9138</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0808 3093 3897 3964 5219 6913 7659 8278 9454 9617</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0530 1397 1709 1751 1935 3103 4365 5231 7789 8512</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wed (2025-12-31)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7136</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0220 0498 1445 2694 3049 4834 5675 6832 6837 9703</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1989 2634 2766 2814 3835 4691 4781 5148 5437 7773</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sat (2026-01-03)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4000 5712 7003 7303 7326 7900 8576 8653 8741 9469</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0171 1284 3640 5248 6183 6591 6824 7649 8183 9499</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sun (2026-01-04)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7713</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0594 1507 1543 4423 5853 6374 6873 7811 9398 9862</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0893 1749 2226 3589 4698 6464 7461 9066 9114 9270</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Wed (2026-01-07)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3912</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0680 1374 1877 2788 7352 7971 9084 9246 9424 9599</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2748 3384 3930 4376 5074 5209 6906 7298 7990 9802</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sat (2026-01-10)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0938</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0946 3775 4265 4337 5262 5479 5864 7786 9330 9825</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0519 1556 1594 5327 5923 6437 6447 6463 8172 9468</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sun (2026-01-11)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0542</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0322 0428 0763 1170 2055 5272 6287 6585 8930 9275</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2521 2587 2847 3066 4097 7583 8375 8546 9165 9196</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Wed (2026-01-14)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0163 0837 1410 2669 2695 3412 4870 9107 9570 9722</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0091 0763 2313 2914 3297 4646 7131 7310 8781 9566</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sat (2026-01-17)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4525</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2176 3267 4737 5552 5858 5919 6016 7978 8143 9945</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0536 0617 2401 3415 4785 4790 6533 8476 8722 9005</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sun (2026-01-18)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8717</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4327</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0267 1152 1190 2645 2751 4695 5471 8295 8822 9422</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0348 1557 2362 3527 5316 5665 6399 6586 7017 8466</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Wed (2026-01-21)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0452</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6502</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0800 0849 1358 2336 4308 5994 6431 8599 9664 9840</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0498 0766 1145 1169 4613 5088 6914 8540 9734 9911</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sat (2026-01-24)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7295</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8557</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0991</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0497 0712 2018 2243 2450 4126 4516 4570 5071 9072</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0055 1872 3177 5379 6437 7133 7530 8184 8328 9735</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sun (2026-01-25)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2772 3296 3596 3963 4594 4734 4960 5259 5968 6585</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0132 0739 1616 1788 2629 2678 6741 7739 9042 9185</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Wed (2026-01-28)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9683</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0617 1179 2808 4724 4932 5337 5514 5919 6193 6388</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1156 1623 3157 3283 3481 4885 5512 5739 6153 6233</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sat (2026-01-31)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7164</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6555</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0249 0285 2225 2628 3631 4235 6547 6661 8293 9354</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3717 4115 4439 5336 6334 6399 6870 7138 9339 9813</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sun (2026-02-01)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7970</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0896</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0553</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1818 2021 3015 4271 4932 6175 8533 9134 9406 9463</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1931 1952 2144 3346 4713 6872 6946 8339 8658 9806</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Wed (2026-02-04)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7541</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0141 1167 1206 1308 3886 4390 4890 5407 8328 8899</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0403 0681 0814 2599 4064 6258 7358 8293 8397 9989</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sat (2026-02-07)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>8047</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>7919</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0743 1239 3077 3246 4394 5148 5232 7734 8070 9023</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0001 0979 1259 2206 3038 4327 6510 6852 7464 7505</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sun (2026-02-08)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4829</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0499</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0549 0720 1015 1949 3329 5154 5428 6868 8532 9052</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2798 3092 3160 3516 3889 4593 5162 6449 7143 7519</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wed (2026-02-11)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7907</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2758</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0289 0590 2947 3579 4505 4730 6961 7206 8057 9002</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0288 0488 1875 1933 2097 2611 5434 7084 7156 9624</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sat (2026-02-14)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9651</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2260 3557 4622 5836 6085 7391 7885 7906 9403 9526</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2191 2345 3760 3761 5221 5574 5668 7802 9228 9419</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sun (2026-02-15)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4374</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>9747</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0747 3029 3168 3386 5071 5410 7525 7719 8008 8640</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0666 1322 2304 2378 3071 3830 7371 7748 8090 9830</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Wed (2026-02-18)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4118</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1325 2632 3185 4698 4953 5273 6083 6437 6470 7708</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0013 0410 1445 2208 4030 4405 5308 6169 8352 9713</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sat (2026-02-21)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8468</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0905 2201 2639 6086 6141 7011 7269 8174 8975 9759</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0674 0891 2191 2681 3449 4271 5815 6044 6467 9011</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sun (2026-02-22)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0041 1203 1695 3950 6171 6410 6540 7219 7440 8236</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1376 1790 2634 3301 4698 5217 5685 7875 9419 9984</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Wed (2026-02-25)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0814 1068 3542 3847 4163 5890 6424 8286 8439 9431</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1511 2357 3115 4586 4965 6034 6445 6473 7266 8196</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sat (2026-02-28)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1002 3679 4256 4411 4486 5987 6901 7127 7232 7897</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0433 0515 2090 2546 4101 4473 4558 6202 8441 9542</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-01)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3927</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2607</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0318 0871 1083 1698 1854 2874 3869 4697 5609 8440</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0483 1995 2792 4408 6217 7338 7340 7953 9154 9595</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-04)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1271 1278 3102 3102 5117 5958 6587 7128 8183 9324</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1121 1394 2964 3616 4339 5612 7597 7609 8088 8251</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-07)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4146</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9274</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0456 1007 1255 3053 4227 4271 6558 7853 8388 9182</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0785 1427 2391 3206 4573 6337 6836 8642 9098 9321</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-08)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0220 1087 1424 3875 3974 4174 6036 6366 7578 9347</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0327 1233 1636 2173 3430 4280 4471 4533 6975 9541</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-11)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7905</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6773</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0073 0338 0732 0820 1651 2331 3707 3877 3927 7246</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1713 2090 3183 3958 4943 6373 7039 8830 9714 9927</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-14)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1366 1904 2415 4165 4899 5947 6695 6881 7273 9269</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0611 2413 3420 4059 4127 5803 8304 9391 9490 9561</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-15)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5747</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>9874</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0412 1147 1243 1985 2179 3468 6074 7024 8159 9891</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0691 2049 3591 3811 6162 6311 6915 8456 8658 9061</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-18)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>8312</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>6146</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0713 0809 2042 2058 2338 2559 3854 4430 7849 9558</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0786 2300 4855 5969 6340 7028 7521 7920 8427 8916</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-21)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0143</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8717</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0220 3505 3661 5006 5126 6010 7114 7245 7272 9358</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0299 1287 3212 3845 4055 7067 8438 9263 9380 9460</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-22)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>8649</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9294</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0277 1339 2592 5108 5223 6046 7821 8860 9683 9791</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0000 1145 1592 2421 2908 3788 3943 6978 7047 9240</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Wed (2026-03-25)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2863</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1171 1245 3789 4773 5448 6016 7877 8176 8965 9184</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1061 1401 2400 5730 6375 6701 7061 7313 8011 9423</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sat (2026-03-28)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8750</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0444</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0197 0205 1556 4091 4596 7159 8360 8612 9036 9710</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0237 0478 1738 1841 2716 3015 3959 8030 9264 9903</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sun (2026-03-29)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6460</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3067 5534 5571 6387 6704 7180 8143 8270 9704 9861</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0108 0274 1223 1754 4293 6178 7396 9123 9361 9602</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Wed (2026-04-01)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0618</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6737</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0687 1092 1236 3723 3913 5002 6418 7977 8240 8912</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0459 5045 5048 5752 5959 5991 6006 6021 6426 8270</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sat (2026-04-04)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7752</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4036</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0060 0228 3161 4052 4115 4838 6112 7981 8416 9834</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0519 0760 1912 3668 4820 4986 6434 8263 8907 9153</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sun (2026-04-05)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0481</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0374 0990 1151 1723 4274 4397 5021 6166 6969 9606</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0618 0703 2365 2635 3107 3264 4862 4964 5175 8753</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Wed (2026-04-08)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0981</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0690 1003 2783 3040 6981 7066 7333 8422 9654 9903</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1498 2877 5563 5708 6278 7415 7749 7804 8824 8959</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sat (2026-04-11)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>8025</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>8453</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0046 0079 0462 2911 4197 6501 7602 9039 9608 9789</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0135 1508 1975 2635 2739 5138 5441 6399 8838 8960</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sun (2026-04-12)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>7083</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>9689</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1175 1219 2128 2636 3209 3346 5433 5928 7175 7289</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3231 3777 4251 4919 5341 5658 5941 6907 8660 8962</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Wed (2026-04-15)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0036 0313 1471 3713 3749 4502 5125 7647 7846 8981</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1927 2196 3334 3868 4546 5295 6303 7138 7501 8160</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sat (2026-04-18)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>8953</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2269 3127 5808 8236 8716 8799 9218 9490 9738 9811</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1791 2091 2581 2858 3176 3503 4887 5993 6619 8230</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sun (2026-04-19)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>9815</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1010 1281 2866 6678 7426 7506 7862 8447 9359 9423</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>3369 5400 6102 6526 6670 6881 9197 9221 9248 9445</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Wed (2026-04-22)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2791</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>9327</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0806 1279 1572 1880 1995 4427 5147 6500 7198 8835</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1495 1597 2043 4436 5645 5992 7546 9726 9889 9927</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sat (2026-04-25)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>9950</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0483 1787 3326 5002 5025 5247 5798 6447 7643 8180</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>4515 5834 7938 8487 8508 8627 8628 8916 9424 9728</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sun (2026-04-26)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7937</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0392 0537 1395 4297 5365 6662 7226 7387 7618 9496</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0897 2492 4036 4736 7069 7273 8977 9351 9398 9777</t>
         </is>
       </c>
     </row>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3072,6 +3072,38 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Wed (2026-04-29)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5729</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2694 5273 6515 7008 7567 7893 9323 9427 9443 9746</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0412 1066 4192 4551 6935 8335 8380 8896 8934 9312</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3072,6 +3072,38 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Thu (2026-04-30)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5729</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2694 5273 6515 7008 7567 7893 9323 9427 9443 9746</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0412 1066 4192 4551 6935 8335 8380 8896 8934 9312</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3104,6 +3104,38 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sat (2026-05-02)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4803</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0705 0855 1297 1337 2506 2660 6208 6677 6989 9480</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0642 0907 1349 2588 3481 4359 4511 5027 5868 6017</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3136,6 +3136,38 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sun (2026-05-03)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5282</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6943</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0773 1703 3869 4550 4899 7136 8197 8810 9048 9907</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1036 1247 1559 1637 2195 2691 3379 8204 9629 9812</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3168,6 +3168,38 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wed (2026-05-06)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3361</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0759 1263 2669 3707 5141 6043 6446 6795 8773 8992</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1585 1612 2778 3062 4651 6123 7092 8016 8395 9696</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3200,6 +3200,38 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sat (2026-05-09)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5740</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0157 1221 1350 2482 3017 3072 4379 5946 9690 9929</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0816 1716 1805 2203 2587 3337 3669 4878 5828 8521</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3232,6 +3232,38 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sun (2026-05-10)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7517</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0047 0081 0327 0431 2259 2585 5535 6906 7976 9624</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0017 0738 1079 2171 2441 2679 2994 4979 6948 8281</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3264,6 +3264,38 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Wed (2026-05-13)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0672</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0496</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6465</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1457 2132 3540 6166 6847 7733 7865 8087 8229 9026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0391 1374 1527 1663 2359 3819 5008 5031 7646 8003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3296,6 +3296,38 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sat (2026-05-16)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>5857</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5182</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2692 2805 5208 5291 6670 7746 8571 8886 9635 9893</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2274 2834 3287 3678 4908 5814 5862 7216 9071 9608</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3328,6 +3328,38 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sun (2026-05-17)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8885</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0777 1776 4532 5227 6823 7075 8441 8802 9205 9672</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1871 2337 2662 3287 3608 5711 5975 6381 9826 9897</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3360,6 +3360,38 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Wed (2026-05-20)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>9517</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>8945</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1117 2873 3075 3722 5479 5720 7057 8567 8736 8812</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0582 0706 2066 2314 2937 4355 4683 7416 9345 9442</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3392,6 +3392,38 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sat (2026-05-23)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0443 1461 2376 4794 4885 5414 6840 6858 8600 9074</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1521 2063 2127 2904 3368 6264 6351 6697 7515 8994</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4d_results_all.xlsx
+++ b/4d_results_all.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3424,6 +3424,38 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sun (2026-05-24)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2668 3546 3745 3787 5918 6392 7101 7874 7953 8473</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0015 2893 3509 3799 4044 5266 6454 7232 7884 8732</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
